--- a/data/trans_orig/P1806_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1806_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses han visitado un podólogo en 2023</t>
+          <t>Población según si en los últimos 12 meses han visitado un podólogo en 2023 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11835</t>
+          <t>12931</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15517</t>
+          <t>14697</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32695</t>
+          <t>32420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20158</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39820</t>
+          <t>39672</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>623606</t>
+          <t>622510</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>632074</t>
+          <t>631848</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>643057</t>
+          <t>643332</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>660235</t>
+          <t>661055</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1271374</t>
+          <t>1271522</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1291036</t>
+          <t>1290463</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24323</t>
+          <t>23654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21963</t>
+          <t>21659</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38846</t>
+          <t>38865</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27740</t>
+          <t>26822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55839</t>
+          <t>55210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1168541</t>
+          <t>1169210</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1186966</t>
+          <t>1187628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>919260</t>
+          <t>919241</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>936143</t>
+          <t>936447</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2095132</t>
+          <t>2095761</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2123231</t>
+          <t>2124149</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16825</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39554</t>
+          <t>40138</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23174</t>
+          <t>21813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65578</t>
+          <t>66458</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45226</t>
+          <t>47337</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91820</t>
+          <t>92377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>665126</t>
+          <t>664542</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>687855</t>
+          <t>687804</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>867222</t>
+          <t>866342</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>909626</t>
+          <t>910987</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1545660</t>
+          <t>1545103</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1592254</t>
+          <t>1590143</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24223</t>
+          <t>23914</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46323</t>
+          <t>47475</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65460</t>
+          <t>63903</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98499</t>
+          <t>97241</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97465</t>
+          <t>97683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135787</t>
+          <t>136690</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>880508</t>
+          <t>879356</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>902608</t>
+          <t>902917</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>995755</t>
+          <t>997013</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1028794</t>
+          <t>1030351</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1885298</t>
+          <t>1884395</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1923620</t>
+          <t>1923402</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60157</t>
+          <t>58876</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102574</t>
+          <t>98977</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>145653</t>
+          <t>144518</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>205827</t>
+          <t>207013</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>223998</t>
+          <t>223470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>295999</t>
+          <t>293469</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3357243</t>
+          <t>3360840</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3399660</t>
+          <t>3400941</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3455086</t>
+          <t>3453900</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3515260</t>
+          <t>3516395</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6824731</t>
+          <t>6827261</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6896732</t>
+          <t>6897260</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1806_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1806_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12931</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21580</t>
+          <t>22733</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14697</t>
+          <t>15720</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32420</t>
+          <t>35102</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>28384</t>
+          <t>30063</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20731</t>
+          <t>21845</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39672</t>
+          <t>41434</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>628637</t>
+          <t>683380</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>622510</t>
+          <t>677724</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>631848</t>
+          <t>687346</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>654172</t>
+          <t>710380</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>643332</t>
+          <t>698011</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>661055</t>
+          <t>717393</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1282810</t>
+          <t>1393760</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1271522</t>
+          <t>1382389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1290463</t>
+          <t>1401978</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13133</t>
+          <t>13438</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23654</t>
+          <t>23798</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29130</t>
+          <t>31047</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21659</t>
+          <t>22948</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38865</t>
+          <t>40654</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>42263</t>
+          <t>44485</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26822</t>
+          <t>34192</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55210</t>
+          <t>58347</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1179731</t>
+          <t>1035479</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1169210</t>
+          <t>1025119</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1187628</t>
+          <t>1041313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>928976</t>
+          <t>1039791</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>919241</t>
+          <t>1030184</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>936447</t>
+          <t>1047890</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2108708</t>
+          <t>2075270</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2095761</t>
+          <t>2061408</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2124149</t>
+          <t>2085563</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26117</t>
+          <t>27400</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40138</t>
+          <t>41198</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>46067</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21813</t>
+          <t>40410</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66458</t>
+          <t>64512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>72184</t>
+          <t>78001</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47337</t>
+          <t>63005</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92377</t>
+          <t>96452</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>678563</t>
+          <t>775673</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>664542</t>
+          <t>761875</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>687804</t>
+          <t>785147</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>886733</t>
+          <t>761062</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>866342</t>
+          <t>747151</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>910987</t>
+          <t>771253</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1565296</t>
+          <t>1536735</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1545103</t>
+          <t>1518284</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1590143</t>
+          <t>1551731</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1637480</t>
+          <t>1614736</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1637480</t>
+          <t>1614736</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1637480</t>
+          <t>1614736</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33573</t>
+          <t>33774</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23914</t>
+          <t>24025</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47475</t>
+          <t>46673</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>82619</t>
+          <t>89756</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63903</t>
+          <t>75690</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97241</t>
+          <t>104941</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>116192</t>
+          <t>123530</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97683</t>
+          <t>106704</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136690</t>
+          <t>144954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>893258</t>
+          <t>956288</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>879356</t>
+          <t>943389</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>902917</t>
+          <t>966037</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1011635</t>
+          <t>1028601</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>997013</t>
+          <t>1013416</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1030351</t>
+          <t>1042667</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1904893</t>
+          <t>1984889</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1884395</t>
+          <t>1963465</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1923402</t>
+          <t>2001715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094254</t>
+          <t>1118357</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094254</t>
+          <t>1118357</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094254</t>
+          <t>1118357</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021085</t>
+          <t>2108419</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021085</t>
+          <t>2108419</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021085</t>
+          <t>2108419</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>79627</t>
+          <t>81942</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58876</t>
+          <t>65067</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98977</t>
+          <t>102269</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>179396</t>
+          <t>194137</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>144518</t>
+          <t>171546</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207013</t>
+          <t>218572</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>259023</t>
+          <t>276079</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>223470</t>
+          <t>246892</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>293469</t>
+          <t>304186</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3380190</t>
+          <t>3450820</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3360840</t>
+          <t>3430493</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3400941</t>
+          <t>3467695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3481517</t>
+          <t>3539833</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3453900</t>
+          <t>3515398</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3516395</t>
+          <t>3562424</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6861707</t>
+          <t>6990653</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6827261</t>
+          <t>6962546</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6897260</t>
+          <t>7019840</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
